--- a/pathway_gene_lists/GOBP_genesets.xlsx
+++ b/pathway_gene_lists/GOBP_genesets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Emma Mask\R_projects\AM14_with_B1-8_comparison\pathway_gene_lists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2342033A-7A0C-4A7E-BB40-4DBDF38A39DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58268652-2245-4B52-BC38-324AB666795B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GOBP_COMPLEMENT_ACTIVATION.v202" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="754">
   <si>
     <t>GOBP_COMPLEMENT_ACTIVATION</t>
   </si>
@@ -2243,6 +2243,45 @@
   </si>
   <si>
     <t>Trim6</t>
+  </si>
+  <si>
+    <t>Gene</t>
+  </si>
+  <si>
+    <t>Epg5</t>
+  </si>
+  <si>
+    <t>Ptpn22</t>
+  </si>
+  <si>
+    <t>Ptprs</t>
+  </si>
+  <si>
+    <t>Nr1h4</t>
+  </si>
+  <si>
+    <t>Gramd4</t>
+  </si>
+  <si>
+    <t>Rab7b</t>
+  </si>
+  <si>
+    <t>Tnip2</t>
+  </si>
+  <si>
+    <t>Cd300ld3</t>
+  </si>
+  <si>
+    <t>Rtn4</t>
+  </si>
+  <si>
+    <t>Tlr9</t>
+  </si>
+  <si>
+    <t>Pik3ap1</t>
+  </si>
+  <si>
+    <t>GOBP_TOLL_LIKE_RECEPTOR_9_SIGNALING_PATHWAY</t>
   </si>
 </sst>
 </file>
@@ -2504,7 +2543,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D636"/>
+  <dimension ref="A1:E636"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
@@ -2513,7 +2552,7 @@
     <col min="4" max="4" width="40.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2526,8 +2565,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2540,8 +2582,11 @@
       <c r="D2" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2554,8 +2599,11 @@
       <c r="D3" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E3" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2568,8 +2616,11 @@
       <c r="D4" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2582,8 +2633,11 @@
       <c r="D5" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2596,8 +2650,11 @@
       <c r="D6" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E6" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2610,8 +2667,11 @@
       <c r="D7" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E7" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2624,8 +2684,11 @@
       <c r="D8" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E8" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2638,8 +2701,11 @@
       <c r="D9" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E9" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2652,8 +2718,11 @@
       <c r="D10" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E10" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2666,8 +2735,11 @@
       <c r="D11" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E11" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -2680,8 +2752,11 @@
       <c r="D12" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E12" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -2694,8 +2769,11 @@
       <c r="D13" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E13" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -2708,8 +2786,11 @@
       <c r="D14" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -2722,8 +2803,11 @@
       <c r="D15" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E15" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2736,8 +2820,11 @@
       <c r="D16" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E16" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -2750,8 +2837,11 @@
       <c r="D17" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E17" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -2764,8 +2854,11 @@
       <c r="D18" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E18" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2779,7 +2872,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2793,7 +2886,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2807,7 +2900,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2821,7 +2914,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2835,7 +2928,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -2849,7 +2942,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2863,7 +2956,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2877,7 +2970,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -2891,7 +2984,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -2905,7 +2998,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -2919,7 +3012,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -2933,7 +3026,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -2947,7 +3040,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>34</v>
       </c>
